--- a/KatalonData/Bootstrap/VT-ACH-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VT-ACH-Data-Prod.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4107" uniqueCount="851">
   <si>
     <t>Notes</t>
   </si>
@@ -1722,6 +1722,873 @@
   </si>
   <si>
     <t>Thu Nov 20 22:32:39 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:40:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:41:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:43:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:44:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:48:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:50:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:51:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:52:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:53:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:54:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:55:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:56:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:58:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:59:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 01:00:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 01:01:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 01:02:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 01:03:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 01:04:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 01:05:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 22:38:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 22:44:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:11:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:12:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:13:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:14:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:15:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:16:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:17:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:32:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:33:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:34:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:35:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:36:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:37:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:38:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:39:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:40:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:41:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:42:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:43:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:44:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:45:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:47:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:48:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:49:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:50:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 00:51:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:58:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:59:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:00:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:01:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:02:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:03:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:04:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:06:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:07:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:08:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:09:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:11:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:12:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:13:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:14:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:15:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:16:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:17:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:18:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:19:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:34:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:37:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:39:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:40:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:41:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 02:42:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:46:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:47:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:48:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 20:49:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 21:16:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 21:17:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 21:18:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 21:19:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:31:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:33:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:34:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:36:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:38:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:39:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:41:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:42:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:44:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:45:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:47:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:48:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:49:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:51:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:53:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:55:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:57:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:59:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 00:00:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 00:02:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 00:04:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 00:06:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 00:08:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 00:09:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 00:11:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 00:12:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 00:13:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:38:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:39:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:41:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:42:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:43:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:44:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:45:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:46:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:47:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:48:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:49:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:50:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:51:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:52:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:54:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:55:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:56:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:57:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:58:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:59:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:00:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:01:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:02:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:04:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:05:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:06:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:07:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:35:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:36:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:37:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 08:38:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:10:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:11:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:12:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:13:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:14:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:15:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:16:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:18:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:18:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:20:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:21:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:22:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:23:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:24:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:25:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:26:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:27:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:28:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:29:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:30:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:32:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:33:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:34:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:35:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:36:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:37:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 23:38:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:50:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:53:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:14:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:15:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:17:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:18:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:19:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:21:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:22:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:23:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:25:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:26:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:27:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 02:29:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:02:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:04:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:06:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:07:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:09:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:10:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:12:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:14:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:15:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:17:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:19:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:21:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:22:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:23:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:25:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:26:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:28:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:29:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:31:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:33:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:35:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:37:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:39:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:40:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:42:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:44:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 23:46:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:53:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:54:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:55:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:56:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:57:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:58:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:59:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:01:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:02:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:03:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:04:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:05:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:06:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:07:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:08:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:09:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:11:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:12:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:13:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:14:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:16:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:17:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:18:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:19:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:20:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:21:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 09:22:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:37:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:38:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:39:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:40:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:41:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:42:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:43:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:44:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:45:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:46:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:47:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:48:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:49:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:50:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:51:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:52:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:53:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:54:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:55:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:56:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:57:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:58:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:59:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 02:00:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 02:01:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 02:02:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 02:03:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:21:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:22:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:23:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:25:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:26:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:27:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:28:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:29:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:30:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:31:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:32:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:34:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:35:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:36:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:37:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:39:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:40:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:41:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:43:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:44:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:45:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:46:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:47:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:48:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:50:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:51:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:52:26 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2187,7 +3054,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>552</v>
+        <v>842</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -3291,7 +4158,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>557</v>
+        <v>847</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -3387,7 +4254,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>558</v>
+        <v>848</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -3483,7 +4350,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>559</v>
+        <v>849</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -3579,7 +4446,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>560</v>
+        <v>850</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -3797,7 +4664,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>553</v>
+        <v>843</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -3893,7 +4760,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>554</v>
+        <v>844</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -3989,7 +4856,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>555</v>
+        <v>845</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -4085,7 +4952,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>556</v>
+        <v>846</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -4301,7 +5168,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>541</v>
+        <v>830</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -4397,7 +5264,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>542</v>
+        <v>831</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -4493,7 +5360,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>543</v>
+        <v>832</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -4589,7 +5456,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>544</v>
+        <v>833</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -4805,10 +5672,10 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>549</v>
+        <v>838</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -4907,10 +5774,10 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>550</v>
+        <v>839</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
@@ -5006,10 +5873,10 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>551</v>
+        <v>840</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -5105,7 +5972,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>525</v>
+        <v>841</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -5324,7 +6191,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>545</v>
+        <v>834</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -5420,7 +6287,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>546</v>
+        <v>835</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -5516,7 +6383,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>547</v>
+        <v>836</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -5612,7 +6479,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>548</v>
+        <v>837</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -5822,7 +6689,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>538</v>
+        <v>827</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -6037,10 +6904,10 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>561</v>
+        <v>829</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -6249,7 +7116,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>539</v>
+        <v>828</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>

--- a/KatalonData/Bootstrap/VT-ACH-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VT-ACH-Data-Prod.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4107" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4215" uniqueCount="878">
   <si>
     <t>Notes</t>
   </si>
@@ -2589,6 +2589,87 @@
   </si>
   <si>
     <t>Wed Mar 11 07:52:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:35:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:36:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:37:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:39:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:40:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:41:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:43:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:44:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:45:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:46:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:48:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:49:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:50:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:51:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:52:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:53:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:55:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:56:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:57:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:58:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:59:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:01:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:02:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:03:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:04:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:05:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:06:58 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3054,7 +3135,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -4158,7 +4239,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>847</v>
+        <v>874</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -4254,7 +4335,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>848</v>
+        <v>875</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -4350,7 +4431,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -4446,7 +4527,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>850</v>
+        <v>877</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -4664,7 +4745,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -4760,7 +4841,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -4856,7 +4937,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -4952,7 +5033,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -5168,7 +5249,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>830</v>
+        <v>857</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -5264,7 +5345,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>831</v>
+        <v>858</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -5360,7 +5441,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>832</v>
+        <v>859</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -5456,7 +5537,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>833</v>
+        <v>860</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -5672,7 +5753,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>838</v>
+        <v>865</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -5774,7 +5855,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>839</v>
+        <v>866</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -5873,7 +5954,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>840</v>
+        <v>867</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -5972,7 +6053,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>841</v>
+        <v>868</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -6191,7 +6272,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>834</v>
+        <v>861</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -6287,7 +6368,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>835</v>
+        <v>862</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -6383,7 +6464,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>836</v>
+        <v>863</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -6479,7 +6560,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>837</v>
+        <v>864</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -6689,7 +6770,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -6904,7 +6985,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -7116,7 +7197,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>

--- a/KatalonData/Bootstrap/VT-ACH-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VT-ACH-Data-Prod.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4215" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4435" uniqueCount="933">
   <si>
     <t>Notes</t>
   </si>
@@ -2670,6 +2670,171 @@
   </si>
   <si>
     <t>Wed Apr 22 22:06:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:33:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:34:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:36:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:37:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:38:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:39:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:40:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:41:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:49:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:50:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:51:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:52:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:53:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:54:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:55:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:56:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:57:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:59:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:00:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:01:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:02:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:04:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:05:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:06:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:08:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:09:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:47:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:48:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:49:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:49:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:50:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:51:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:52:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:54:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:55:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:56:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:57:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:58:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:59:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:14:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:15:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:16:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:17:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:18:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:19:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:20:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:35:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:36:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:37:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:38:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:39:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:58:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:59:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 22:00:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 22:01:46 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3135,7 +3300,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>869</v>
+        <v>921</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -4239,7 +4404,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>874</v>
+        <v>925</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -4335,7 +4500,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>875</v>
+        <v>926</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -4431,7 +4596,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>876</v>
+        <v>927</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -4527,7 +4692,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>877</v>
+        <v>928</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -4745,7 +4910,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>870</v>
+        <v>929</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -4841,7 +5006,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>871</v>
+        <v>930</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -4937,7 +5102,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>872</v>
+        <v>931</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -5033,7 +5198,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>873</v>
+        <v>932</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -5249,7 +5414,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>857</v>
+        <v>910</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -5345,7 +5510,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>858</v>
+        <v>911</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -5441,7 +5606,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>859</v>
+        <v>912</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -5537,7 +5702,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>860</v>
+        <v>913</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -5753,7 +5918,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>865</v>
+        <v>917</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -5855,7 +6020,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>866</v>
+        <v>918</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -5954,7 +6119,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>867</v>
+        <v>919</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -6053,7 +6218,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>868</v>
+        <v>920</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -6272,7 +6437,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>861</v>
+        <v>914</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -6368,7 +6533,7 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>862</v>
+        <v>915</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -6464,7 +6629,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>863</v>
+        <v>916</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -6560,7 +6725,7 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -6770,7 +6935,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>854</v>
+        <v>907</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -6985,7 +7150,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>856</v>
+        <v>909</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -7197,7 +7362,7 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>855</v>
+        <v>908</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>

--- a/KatalonData/Bootstrap/VT-ACH-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VT-ACH-Data-Prod.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4435" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4705" uniqueCount="1068">
   <si>
     <t>Notes</t>
   </si>
@@ -2835,6 +2835,411 @@
   </si>
   <si>
     <t>Fri Jun 19 22:01:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:11:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:12:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:13:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:14:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:15:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:16:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:17:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:18:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:19:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:20:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:21:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:22:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:23:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:24:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:26:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:27:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:28:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:29:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:30:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:31:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:32:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:33:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:34:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:35:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:36:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:37:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:38:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:37:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:38:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:39:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:40:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:41:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:42:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:43:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:44:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:45:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:46:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:47:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:48:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:49:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:50:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:51:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:52:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:53:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:54:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:55:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:56:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:57:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:58:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:59:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:00:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:01:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:02:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:03:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:41:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:42:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:43:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:44:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:46:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:47:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:48:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:49:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:51:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:52:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:53:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:54:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:55:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:56:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:58:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:59:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:00:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:02:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:03:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:04:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:06:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:07:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:08:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:09:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:11:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:12:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:14:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:11:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:12:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:13:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:14:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:16:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:17:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:18:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:19:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:21:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:22:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:23:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:24:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:26:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:27:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:28:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:29:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:31:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:32:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:33:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:35:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:36:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:37:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:39:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:40:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:41:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:42:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:44:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:07:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:08:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:09:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:11:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:12:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:13:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:14:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:16:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:17:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:18:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:19:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:21:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:22:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:23:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:24:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:26:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:27:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:28:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:29:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:30:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:32:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:33:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:34:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:35:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:37:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:38:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:39:27 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3181,7 +3586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="48.85546875" collapsed="true"/>
@@ -3296,13 +3701,13 @@
       </c>
     </row>
     <row ht="60" r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B2" t="s">
-        <v>921</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>1059</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E2" s="1"/>
@@ -3674,7 +4079,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988FEDBD-7F22-4A81-874A-3DEFCF16E7A5}">
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row ht="30" r="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -3878,7 +4283,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE5B7A4-4B6A-47F5-96A4-B3E5E3DE3031}">
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row ht="30" r="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -4082,7 +4487,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2222826C-56BD-45AE-94B1-557604E55906}">
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row ht="30" r="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -4286,7 +4691,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E504F0BC-EC73-4189-9C9D-13EC19AB7067}">
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="36.140625" collapsed="true"/>
@@ -4400,13 +4805,13 @@
       </c>
     </row>
     <row ht="60" r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B2" t="s">
-        <v>925</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>1064</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E2" s="1"/>
@@ -4496,13 +4901,13 @@
       </c>
     </row>
     <row ht="60" r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B3" t="s">
-        <v>926</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
+        <v>1065</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E3" s="1"/>
@@ -4592,13 +4997,13 @@
       </c>
     </row>
     <row ht="60" r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B4" t="s">
-        <v>927</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>1066</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E4" s="1"/>
@@ -4688,13 +5093,13 @@
       </c>
     </row>
     <row ht="60" r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B5" t="s">
-        <v>928</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="0">
+        <v>1067</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E5" s="1"/>
@@ -4790,7 +5195,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A4F0C9-A136-4AAE-9CDA-286E007D3412}">
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="25.28515625" collapsed="true"/>
@@ -4906,13 +5311,13 @@
       </c>
     </row>
     <row ht="45" r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B2" t="s">
-        <v>929</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>1060</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E2" s="1"/>
@@ -5002,13 +5407,13 @@
       </c>
     </row>
     <row ht="45" r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B3" t="s">
-        <v>930</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
+        <v>1061</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E3" s="1"/>
@@ -5098,13 +5503,13 @@
       </c>
     </row>
     <row ht="45" r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B4" t="s">
-        <v>931</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>1062</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E4" s="1"/>
@@ -5194,13 +5599,13 @@
       </c>
     </row>
     <row ht="45" r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B5" t="s">
-        <v>932</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="0">
+        <v>1063</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E5" s="1"/>
@@ -5296,7 +5701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB8DBA0-6E12-40A7-A154-812E9C7558EE}">
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="30.28515625" collapsed="true"/>
@@ -5410,13 +5815,13 @@
       </c>
     </row>
     <row ht="60" r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B2" t="s">
-        <v>910</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>1047</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E2" s="1"/>
@@ -5506,13 +5911,13 @@
       </c>
     </row>
     <row ht="60" r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B3" t="s">
-        <v>911</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
+        <v>1048</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E3" s="1"/>
@@ -5602,13 +6007,13 @@
       </c>
     </row>
     <row ht="60" r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B4" t="s">
-        <v>912</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>1049</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E4" s="1"/>
@@ -5698,13 +6103,13 @@
       </c>
     </row>
     <row ht="60" r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B5" t="s">
-        <v>913</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="0">
+        <v>1050</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E5" s="1"/>
@@ -5800,7 +6205,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A032A2-FBCF-4DA0-9FFF-706908293773}">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row ht="45" r="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -5914,13 +6319,13 @@
       </c>
     </row>
     <row ht="60" r="2" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B2" t="s">
-        <v>917</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>1055</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E2" s="1"/>
@@ -6011,18 +6416,18 @@
       <c r="AJ2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AP2">
+      <c r="AP2" s="0">
         <v>0</v>
       </c>
     </row>
     <row ht="60" r="3" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B3" t="s">
-        <v>918</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
+        <v>1056</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E3" s="1"/>
@@ -6115,13 +6520,13 @@
       </c>
     </row>
     <row ht="60" r="4" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B4" t="s">
-        <v>919</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>1057</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E4" s="1"/>
@@ -6214,13 +6619,13 @@
       </c>
     </row>
     <row ht="60" r="5" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B5" t="s">
-        <v>920</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="0">
+        <v>1058</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E5" s="1"/>
@@ -6319,7 +6724,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6202EF1D-4DA5-4B12-BF3F-FAC0A7785CB1}">
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="25.140625" collapsed="true"/>
@@ -6433,13 +6838,13 @@
       </c>
     </row>
     <row ht="45" r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B2" t="s">
-        <v>914</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>1051</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E2" s="1"/>
@@ -6529,13 +6934,13 @@
       </c>
     </row>
     <row ht="45" r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B3" t="s">
-        <v>915</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
+        <v>1052</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E3" s="1"/>
@@ -6625,13 +7030,13 @@
       </c>
     </row>
     <row ht="45" r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>1053</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E4" s="1"/>
@@ -6721,13 +7126,13 @@
       </c>
     </row>
     <row ht="45" r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B5" t="s">
-        <v>890</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" t="s" s="0">
+        <v>1054</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E5" s="1"/>
@@ -6823,7 +7228,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{882B148C-EFD9-44D0-90C1-C2782B34D7E4}">
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row ht="30" r="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -6931,13 +7336,13 @@
       </c>
     </row>
     <row ht="90" r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B2" t="s">
-        <v>907</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>1044</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E2" s="1"/>
@@ -7032,7 +7437,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A10D9D9-1102-4A53-862F-47C2BA74C489}">
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="25.28515625" collapsed="true"/>
@@ -7146,13 +7551,13 @@
       </c>
     </row>
     <row ht="90" r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B2" t="s">
-        <v>909</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>1046</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E2" s="1"/>
@@ -7250,7 +7655,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A77B7693-1BD8-4C1F-8F19-2C5EC4387133}">
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row ht="30" r="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -7358,13 +7763,13 @@
       </c>
     </row>
     <row ht="90" r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B2" t="s">
-        <v>908</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>1045</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E2" s="1"/>
